--- a/simulation/dac/dac_mass_flow_data.xlsx
+++ b/simulation/dac/dac_mass_flow_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Propanol production\simulation\dac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96FF361-56A8-406D-84A8-973E929AA4BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEBF361-7EC7-4DC7-81F6-6F1A12121EF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="6585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="6585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="material_streams" sheetId="1" r:id="rId1"/>
@@ -679,11 +679,11 @@
         <v>10</v>
       </c>
       <c r="D7" s="14">
-        <v>774.44961811444705</v>
+        <v>148.79163130681701</v>
       </c>
       <c r="E7" s="18">
         <f t="shared" si="0"/>
-        <v>6.1986160194061453E-2</v>
+        <v>1.1909130920840772E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -697,11 +697,11 @@
         <v>10</v>
       </c>
       <c r="D8" s="14">
-        <v>12614.907530013799</v>
+        <v>539.17127004946599</v>
       </c>
       <c r="E8" s="18">
         <f t="shared" si="0"/>
-        <v>1.0096843754568836</v>
+        <v>4.3154720378960579E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -715,11 +715,11 @@
         <v>11</v>
       </c>
       <c r="D9" s="14">
-        <v>17154.742873839001</v>
+        <v>4435.2150659924</v>
       </c>
       <c r="E9" s="18">
         <f t="shared" si="0"/>
-        <v>1.3730481815649591</v>
+        <v>0.35499010541844206</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
